--- a/exports/trend_1d/SUNPHARMA_full_report.xlsx
+++ b/exports/trend_1d/SUNPHARMA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>4.85</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42060</v>
+        <v>42061</v>
       </c>
       <c r="H2" t="n">
-        <v>890.75</v>
+        <v>865.7</v>
       </c>
       <c r="I2" t="n">
         <v>887.5457781761484</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
-        <v>7.85</v>
+        <v>4.82</v>
       </c>
       <c r="L2" t="n">
         <v>0.79</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>9.31</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42066</v>
+        <v>42067</v>
       </c>
       <c r="H3" t="n">
-        <v>943.05</v>
+        <v>1006.3</v>
       </c>
       <c r="I3" t="n">
         <v>943.8795473787388</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.93</v>
+        <v>-16.24</v>
       </c>
       <c r="L3" t="n">
-        <v>9.9</v>
+        <v>19.67</v>
       </c>
       <c r="M3" t="n">
         <v>3.78</v>
       </c>
       <c r="N3" t="n">
-        <v>5.27</v>
+        <v>6.71</v>
       </c>
       <c r="O3" t="n">
         <v>-2.81</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>11.74</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42114</v>
+        <v>42115</v>
       </c>
       <c r="H4" t="n">
-        <v>1043.8</v>
+        <v>952.2</v>
       </c>
       <c r="I4" t="n">
         <v>1036.296281559853</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K4" t="n">
-        <v>3.73</v>
+        <v>-5.38</v>
       </c>
       <c r="L4" t="n">
-        <v>6.81</v>
+        <v>7.58</v>
       </c>
       <c r="M4" t="n">
-        <v>1.39</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>4.61</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="O4" t="n">
         <v>6.71</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>16.45</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42194</v>
+        <v>42195</v>
       </c>
       <c r="H5" t="n">
-        <v>872.4</v>
+        <v>901.55</v>
       </c>
       <c r="I5" t="n">
         <v>897.9623749154337</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K5" t="n">
-        <v>8.380000000000001</v>
+        <v>5.32</v>
       </c>
       <c r="L5" t="n">
         <v>6.07</v>
@@ -726,7 +785,7 @@
         <v>1.26</v>
       </c>
       <c r="N5" t="n">
-        <v>2.97</v>
+        <v>3.34</v>
       </c>
       <c r="O5" t="n">
         <v>-8.779999999999999</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42205</v>
+        <v>42206</v>
       </c>
       <c r="H6" t="n">
-        <v>948</v>
+        <v>805.25</v>
       </c>
       <c r="I6" t="n">
         <v>893.0841056442789</v>
       </c>
       <c r="J6" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-10.68</v>
+      </c>
+      <c r="L6" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="M6" t="n">
         <v>10</v>
       </c>
-      <c r="K6" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.01</v>
-      </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>15.06</v>
       </c>
       <c r="O6" t="n">
         <v>3.34</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>14.34</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42229</v>
+        <v>42230</v>
       </c>
       <c r="H7" t="n">
-        <v>879.05</v>
+        <v>897.7</v>
       </c>
       <c r="I7" t="n">
         <v>893.8397597025657</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.16</v>
+        <v>-11.48</v>
       </c>
       <c r="L7" t="n">
-        <v>10.28</v>
+        <v>13.59</v>
       </c>
       <c r="M7" t="n">
         <v>1.14</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.43</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42250</v>
+        <v>42251</v>
       </c>
       <c r="H8" t="n">
-        <v>884.95</v>
+        <v>857.7</v>
       </c>
       <c r="I8" t="n">
         <v>861.2968311260689</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.42</v>
+        <v>-4.46</v>
       </c>
       <c r="L8" t="n">
         <v>5.31</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>14.02</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42283</v>
+        <v>42284</v>
       </c>
       <c r="H9" t="n">
-        <v>909.95</v>
+        <v>926.2</v>
       </c>
       <c r="I9" t="n">
         <v>925.2430280291985</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.09</v>
+        <v>-7.99</v>
       </c>
       <c r="L9" t="n">
-        <v>7.36</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M9" t="n">
         <v>1.45</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>8.94</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42312</v>
+        <v>42313</v>
       </c>
       <c r="H10" t="n">
-        <v>852.5</v>
+        <v>815.95</v>
       </c>
       <c r="I10" t="n">
         <v>850.0597513161348</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.96</v>
+        <v>-11.9</v>
       </c>
       <c r="L10" t="n">
-        <v>8.23</v>
+        <v>12.65</v>
       </c>
       <c r="M10" t="n">
         <v>1.63</v>
       </c>
       <c r="N10" t="n">
-        <v>2.72</v>
+        <v>4.29</v>
       </c>
       <c r="O10" t="n">
         <v>1.79</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.11</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42342</v>
+        <v>42345</v>
       </c>
       <c r="H11" t="n">
-        <v>755.4</v>
+        <v>777.35</v>
       </c>
       <c r="I11" t="n">
         <v>774.7181495486816</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K11" t="n">
-        <v>7.42</v>
+        <v>4.73</v>
       </c>
       <c r="L11" t="n">
         <v>4.16</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42457</v>
+        <v>42458</v>
       </c>
       <c r="H12" t="n">
-        <v>809.25</v>
+        <v>794.35</v>
       </c>
       <c r="I12" t="n">
         <v>802.9672606124486</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>2.19</v>
       </c>
       <c r="L12" t="n">
         <v>5.96</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42516</v>
+        <v>42517</v>
       </c>
       <c r="H13" t="n">
-        <v>779.35</v>
+        <v>824.95</v>
       </c>
       <c r="I13" t="n">
         <v>818.0961762278895</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K13" t="n">
-        <v>1.89</v>
+        <v>-3.85</v>
       </c>
       <c r="L13" t="n">
         <v>5.89</v>
@@ -1182,7 +1337,7 @@
         <v>2.65</v>
       </c>
       <c r="N13" t="n">
-        <v>2.18</v>
+        <v>5.85</v>
       </c>
       <c r="O13" t="n">
         <v>-1.84</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>8.16</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42520</v>
+        <v>42521</v>
       </c>
       <c r="H14" t="n">
-        <v>812.1</v>
+        <v>762.75</v>
       </c>
       <c r="I14" t="n">
         <v>768.7339587768817</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.56</v>
+        <v>-7.54</v>
       </c>
       <c r="L14" t="n">
-        <v>4.22</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="N14" t="n">
-        <v>1.56</v>
+        <v>6.08</v>
       </c>
       <c r="O14" t="n">
         <v>5.85</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.79</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42559</v>
+        <v>42562</v>
       </c>
       <c r="H15" t="n">
-        <v>777.5</v>
+        <v>789</v>
       </c>
       <c r="I15" t="n">
         <v>781.8064637610503</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.93</v>
+        <v>-3.44</v>
       </c>
       <c r="L15" t="n">
         <v>4.75</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.57</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42594</v>
+        <v>42598</v>
       </c>
       <c r="H16" t="n">
-        <v>800.55</v>
+        <v>782.7</v>
       </c>
       <c r="I16" t="n">
         <v>796.361181473429</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K16" t="n">
-        <v>1.46</v>
+        <v>-0.8</v>
       </c>
       <c r="L16" t="n">
         <v>3.16</v>
@@ -1353,7 +1544,7 @@
         <v>0.5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.41</v>
+        <v>2.23</v>
       </c>
       <c r="O16" t="n">
         <v>1.48</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42620</v>
+        <v>42621</v>
       </c>
       <c r="H17" t="n">
-        <v>779.25</v>
+        <v>808.05</v>
       </c>
       <c r="I17" t="n">
         <v>805.6657135771167</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K17" t="n">
-        <v>0.44</v>
+        <v>-3.24</v>
       </c>
       <c r="L17" t="n">
-        <v>3.28</v>
+        <v>3.46</v>
       </c>
       <c r="M17" t="n">
         <v>0.97</v>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
         <v>-2.23</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>7.93</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H18" t="n">
-        <v>764.8</v>
+        <v>735.85</v>
       </c>
       <c r="I18" t="n">
         <v>754.3914743297994</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.35</v>
+        <v>-8.94</v>
       </c>
       <c r="L18" t="n">
-        <v>5.53</v>
+        <v>9.41</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>1.78</v>
+        <v>3.79</v>
       </c>
       <c r="O18" t="n">
         <v>3.7</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42698</v>
+        <v>42699</v>
       </c>
       <c r="H19" t="n">
-        <v>682.5</v>
+        <v>714.15</v>
       </c>
       <c r="I19" t="n">
         <v>704.4185008428757</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K19" t="n">
-        <v>7.25</v>
+        <v>2.95</v>
       </c>
       <c r="L19" t="n">
         <v>5.05</v>
@@ -1524,7 +1751,7 @@
         <v>3.76</v>
       </c>
       <c r="N19" t="n">
-        <v>3.99</v>
+        <v>4.64</v>
       </c>
       <c r="O19" t="n">
         <v>-3.79</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>12.96</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42718</v>
+        <v>42719</v>
       </c>
       <c r="H20" t="n">
-        <v>678.4</v>
+        <v>649.95</v>
       </c>
       <c r="I20" t="n">
         <v>657.969717307644</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.01</v>
+        <v>-8.99</v>
       </c>
       <c r="L20" t="n">
-        <v>7.74</v>
+        <v>9.68</v>
       </c>
       <c r="M20" t="n">
         <v>0.87</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>11.46</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42769</v>
+        <v>42772</v>
       </c>
       <c r="H21" t="n">
-        <v>647.25</v>
+        <v>675.15</v>
       </c>
       <c r="I21" t="n">
         <v>669.4659753757169</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K21" t="n">
-        <v>0.42</v>
+        <v>-3.88</v>
       </c>
       <c r="L21" t="n">
-        <v>3.64</v>
+        <v>4.21</v>
       </c>
       <c r="M21" t="n">
         <v>1.37</v>
       </c>
       <c r="N21" t="n">
-        <v>2.53</v>
+        <v>4.31</v>
       </c>
       <c r="O21" t="n">
         <v>-4.19</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>9.27</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42780</v>
+        <v>42781</v>
       </c>
       <c r="H22" t="n">
-        <v>649.3</v>
+        <v>623.05</v>
       </c>
       <c r="I22" t="n">
         <v>627.9714260559922</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.83</v>
+        <v>-7.72</v>
       </c>
       <c r="L22" t="n">
-        <v>5.07</v>
+        <v>7.95</v>
       </c>
       <c r="M22" t="n">
         <v>0.14</v>
       </c>
       <c r="N22" t="n">
-        <v>1.11</v>
+        <v>4.04</v>
       </c>
       <c r="O22" t="n">
         <v>4.31</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>10.75</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>42794</v>
+        <v>42795</v>
       </c>
       <c r="H23" t="n">
-        <v>679</v>
+        <v>694.65</v>
       </c>
       <c r="I23" t="n">
         <v>690.0533818403775</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.98</v>
+        <v>-11.49</v>
       </c>
       <c r="L23" t="n">
-        <v>10.17</v>
+        <v>11.93</v>
       </c>
       <c r="M23" t="n">
         <v>0.65</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>8.15</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>42844</v>
+        <v>42845</v>
       </c>
       <c r="H24" t="n">
-        <v>663.35</v>
+        <v>655.95</v>
       </c>
       <c r="I24" t="n">
         <v>660.3369135688129</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.51</v>
+        <v>-5.57</v>
       </c>
       <c r="L24" t="n">
-        <v>4.82</v>
+        <v>5.7</v>
       </c>
       <c r="M24" t="n">
         <v>1.55</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.65</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>42928</v>
+        <v>42929</v>
       </c>
       <c r="H25" t="n">
-        <v>562.4</v>
+        <v>569.3</v>
       </c>
       <c r="I25" t="n">
         <v>565.0628599154536</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K25" t="n">
-        <v>14.26</v>
+        <v>13.21</v>
       </c>
       <c r="L25" t="n">
         <v>1.79</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>7.44</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>42944</v>
+        <v>42947</v>
       </c>
       <c r="H26" t="n">
-        <v>550.8</v>
+        <v>531.65</v>
       </c>
       <c r="I26" t="n">
         <v>548.9543247201722</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.25</v>
+        <v>-6.61</v>
       </c>
       <c r="L26" t="n">
-        <v>3.57</v>
+        <v>7.1</v>
       </c>
       <c r="M26" t="n">
         <v>0.54</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>10</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>42991</v>
+        <v>42992</v>
       </c>
       <c r="H27" t="n">
-        <v>503.35</v>
+        <v>524.65</v>
       </c>
       <c r="I27" t="n">
         <v>507.0612882040246</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K27" t="n">
-        <v>5.32</v>
+        <v>1.32</v>
       </c>
       <c r="L27" t="n">
         <v>4.15</v>
       </c>
       <c r="M27" t="n">
-        <v>1.62</v>
+        <v>3.31</v>
       </c>
       <c r="N27" t="n">
         <v>4.84</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>11.07</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43053</v>
+        <v>43054</v>
       </c>
       <c r="H28" t="n">
-        <v>526.05</v>
+        <v>504.65</v>
       </c>
       <c r="I28" t="n">
         <v>514.0014232590778</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K28" t="n">
-        <v>0.27</v>
+        <v>-3.81</v>
       </c>
       <c r="L28" t="n">
         <v>6.7</v>
       </c>
       <c r="M28" t="n">
-        <v>1.23</v>
+        <v>1.91</v>
       </c>
       <c r="N28" t="n">
-        <v>2.54</v>
+        <v>4.07</v>
       </c>
       <c r="O28" t="n">
         <v>4.23</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>12.62</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43095</v>
+        <v>43096</v>
       </c>
       <c r="H29" t="n">
-        <v>541.3</v>
+        <v>576.3</v>
       </c>
       <c r="I29" t="n">
         <v>555.7325570730571</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.26</v>
+        <v>-14.2</v>
       </c>
       <c r="L29" t="n">
-        <v>10.24</v>
+        <v>15.27</v>
       </c>
       <c r="M29" t="n">
         <v>0.9</v>
       </c>
       <c r="N29" t="n">
-        <v>4.04</v>
+        <v>6.47</v>
       </c>
       <c r="O29" t="n">
         <v>-4.07</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>10.79</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43151</v>
+        <v>43152</v>
       </c>
       <c r="H30" t="n">
-        <v>559.5</v>
+        <v>525.75</v>
       </c>
       <c r="I30" t="n">
         <v>545.2673374309873</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.92</v>
+        <v>-8.77</v>
       </c>
       <c r="L30" t="n">
-        <v>7.83</v>
+        <v>11.28</v>
       </c>
       <c r="M30" t="n">
         <v>3.67</v>
       </c>
       <c r="N30" t="n">
-        <v>4.41</v>
+        <v>6.03</v>
       </c>
       <c r="O30" t="n">
         <v>6.47</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>15.4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43245</v>
+        <v>43248</v>
       </c>
       <c r="H31" t="n">
-        <v>466.45</v>
+        <v>499.7</v>
       </c>
       <c r="I31" t="n">
         <v>498.2586034496168</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K31" t="n">
-        <v>11.28</v>
+        <v>4.95</v>
       </c>
       <c r="L31" t="n">
         <v>9.42</v>
       </c>
       <c r="M31" t="n">
-        <v>3.07</v>
+        <v>3.98</v>
       </c>
       <c r="N31" t="n">
-        <v>5.21</v>
+        <v>7.13</v>
       </c>
       <c r="O31" t="n">
         <v>-6.03</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>12.82</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43376</v>
+        <v>43377</v>
       </c>
       <c r="H32" t="n">
-        <v>620.85</v>
+        <v>599.05</v>
       </c>
       <c r="I32" t="n">
         <v>617.9461732081835</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K32" t="n">
-        <v>24.24</v>
+        <v>19.88</v>
       </c>
       <c r="L32" t="n">
         <v>5.91</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.84</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H33" t="n">
-        <v>447.35</v>
+        <v>455.9</v>
       </c>
       <c r="I33" t="n">
         <v>449.2880590758236</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K33" t="n">
-        <v>25.32</v>
+        <v>23.9</v>
       </c>
       <c r="L33" t="n">
         <v>3.62</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H34" t="n">
-        <v>448.2</v>
+        <v>439.15</v>
       </c>
       <c r="I34" t="n">
         <v>443.317033617501</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.69</v>
+        <v>-3.67</v>
       </c>
       <c r="L34" t="n">
-        <v>2.31</v>
+        <v>4.92</v>
       </c>
       <c r="M34" t="n">
         <v>1.42</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.5</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43658</v>
+        <v>43661</v>
       </c>
       <c r="H35" t="n">
-        <v>407.7</v>
+        <v>422.95</v>
       </c>
       <c r="I35" t="n">
         <v>412.0637677964837</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K35" t="n">
-        <v>7.16</v>
+        <v>3.69</v>
       </c>
       <c r="L35" t="n">
         <v>2.44</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>11.05</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43735</v>
+        <v>43738</v>
       </c>
       <c r="H36" t="n">
-        <v>401.7</v>
+        <v>389.45</v>
       </c>
       <c r="I36" t="n">
         <v>397.6762693697237</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.02</v>
+        <v>-7.92</v>
       </c>
       <c r="L36" t="n">
-        <v>5.37</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M36" t="n">
         <v>3.5</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>11.87</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43765</v>
+        <v>43767</v>
       </c>
       <c r="H37" t="n">
-        <v>417.75</v>
+        <v>421.95</v>
       </c>
       <c r="I37" t="n">
         <v>421.0337114356494</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.27</v>
+        <v>-8.35</v>
       </c>
       <c r="L37" t="n">
-        <v>7.79</v>
+        <v>9.26</v>
       </c>
       <c r="M37" t="n">
         <v>0.65</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.96</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H38" t="n">
-        <v>434.3</v>
+        <v>422.8</v>
       </c>
       <c r="I38" t="n">
         <v>427.9062123039217</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K38" t="n">
-        <v>2.93</v>
+        <v>0.2</v>
       </c>
       <c r="L38" t="n">
         <v>3.52</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>8.81</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43924</v>
+        <v>43928</v>
       </c>
       <c r="H39" t="n">
-        <v>375.95</v>
+        <v>417.35</v>
       </c>
       <c r="I39" t="n">
         <v>410.0115728896493</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K39" t="n">
-        <v>11.08</v>
+        <v>1.29</v>
       </c>
       <c r="L39" t="n">
         <v>4.48</v>
       </c>
       <c r="M39" t="n">
-        <v>4.99</v>
+        <v>5.87</v>
       </c>
       <c r="N39" t="n">
-        <v>9.43</v>
+        <v>11.01</v>
       </c>
       <c r="O39" t="n">
         <v>-2.65</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>24.69</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44081</v>
+        <v>44082</v>
       </c>
       <c r="H40" t="n">
-        <v>513.25</v>
+        <v>501.9</v>
       </c>
       <c r="I40" t="n">
         <v>505.0911875236453</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K40" t="n">
-        <v>22.98</v>
+        <v>20.26</v>
       </c>
       <c r="L40" t="n">
         <v>6.96</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>11.97</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44138</v>
+        <v>44139</v>
       </c>
       <c r="H41" t="n">
-        <v>485.6</v>
+        <v>504.65</v>
       </c>
       <c r="I41" t="n">
         <v>497.1430263567825</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K41" t="n">
-        <v>3.25</v>
+        <v>-0.55</v>
       </c>
       <c r="L41" t="n">
         <v>6.59</v>
       </c>
       <c r="M41" t="n">
-        <v>2.29</v>
+        <v>2.94</v>
       </c>
       <c r="N41" t="n">
         <v>4.18</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.08</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44217</v>
+        <v>44218</v>
       </c>
       <c r="H42" t="n">
-        <v>582.9</v>
+        <v>575.2</v>
       </c>
       <c r="I42" t="n">
         <v>575.2418821163603</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K42" t="n">
-        <v>15.51</v>
+        <v>13.98</v>
       </c>
       <c r="L42" t="n">
         <v>3.1</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44229</v>
+        <v>44230</v>
       </c>
       <c r="H43" t="n">
-        <v>609.45</v>
+        <v>629.2</v>
       </c>
       <c r="I43" t="n">
         <v>619.4726817765588</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.95</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>7.25</v>
+        <v>12.73</v>
       </c>
       <c r="M43" t="n">
         <v>1.67</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.27</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H44" t="n">
-        <v>790.65</v>
+        <v>770.75</v>
       </c>
       <c r="I44" t="n">
         <v>786.1192029664578</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="K44" t="n">
-        <v>25.66</v>
+        <v>22.5</v>
       </c>
       <c r="L44" t="n">
         <v>10.66</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>196</v>
+        <v>197</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>10</v>
+      </c>
+      <c r="U44" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.4</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44557</v>
+        <v>44558</v>
       </c>
       <c r="H45" t="n">
-        <v>794.1</v>
+        <v>815.1</v>
       </c>
       <c r="I45" t="n">
         <v>808.0304706246488</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.03</v>
+        <v>-5.75</v>
       </c>
       <c r="L45" t="n">
-        <v>4.31</v>
+        <v>6.38</v>
       </c>
       <c r="M45" t="n">
         <v>1.47</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>8.48</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H46" t="n">
-        <v>808.75</v>
+        <v>800.85</v>
       </c>
       <c r="I46" t="n">
         <v>804.7159181144361</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.78</v>
+        <v>-1.75</v>
       </c>
       <c r="L46" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="M46" t="n">
-        <v>0.43</v>
+        <v>0.59</v>
       </c>
       <c r="N46" t="n">
         <v>2.21</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44592</v>
+        <v>44593</v>
       </c>
       <c r="H47" t="n">
-        <v>834.5</v>
+        <v>891.75</v>
       </c>
       <c r="I47" t="n">
         <v>862.4077812202113</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.2</v>
+        <v>-11.35</v>
       </c>
       <c r="L47" t="n">
-        <v>6.11</v>
+        <v>11.76</v>
       </c>
       <c r="M47" t="n">
-        <v>0.48</v>
+        <v>1.55</v>
       </c>
       <c r="N47" t="n">
-        <v>1.88</v>
+        <v>6.86</v>
       </c>
       <c r="O47" t="n">
         <v>-0.98</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>11.86</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H48" t="n">
-        <v>840.25</v>
+        <v>818.25</v>
       </c>
       <c r="I48" t="n">
         <v>825.1174752955897</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.78</v>
+        <v>-8.24</v>
       </c>
       <c r="L48" t="n">
-        <v>7.53</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M48" t="n">
         <v>1.15</v>
       </c>
       <c r="N48" t="n">
-        <v>2.21</v>
+        <v>2.62</v>
       </c>
       <c r="O48" t="n">
         <v>6.86</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44630</v>
+        <v>44631</v>
       </c>
       <c r="H49" t="n">
-        <v>869.55</v>
+        <v>902</v>
       </c>
       <c r="I49" t="n">
         <v>883.8168345538185</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.27</v>
+        <v>-10.24</v>
       </c>
       <c r="L49" t="n">
-        <v>8.26</v>
+        <v>10.85</v>
       </c>
       <c r="M49" t="n">
         <v>1.45</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>9.76</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44690</v>
+        <v>44691</v>
       </c>
       <c r="H50" t="n">
-        <v>885.4</v>
+        <v>861.85</v>
       </c>
       <c r="I50" t="n">
         <v>877.2499909574132</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.84</v>
+        <v>-4.45</v>
       </c>
       <c r="L50" t="n">
-        <v>4.49</v>
+        <v>6.15</v>
       </c>
       <c r="M50" t="n">
         <v>1.84</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.55</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44755</v>
+        <v>44756</v>
       </c>
       <c r="H51" t="n">
-        <v>860.15</v>
+        <v>879.9</v>
       </c>
       <c r="I51" t="n">
         <v>866.6147610884734</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K51" t="n">
-        <v>0.2</v>
+        <v>-2.09</v>
       </c>
       <c r="L51" t="n">
         <v>8.06</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.38</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44902</v>
+        <v>44903</v>
       </c>
       <c r="H52" t="n">
-        <v>1017.75</v>
+        <v>980.8</v>
       </c>
       <c r="I52" t="n">
         <v>995.6534002384288</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K52" t="n">
-        <v>15.67</v>
+        <v>11.47</v>
       </c>
       <c r="L52" t="n">
         <v>2.67</v>
@@ -3405,7 +4028,7 @@
         <v>1.17</v>
       </c>
       <c r="N52" t="n">
-        <v>2.6</v>
+        <v>3.63</v>
       </c>
       <c r="O52" t="n">
         <v>2.3</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>6</v>
+      </c>
+      <c r="U52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>7.78</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44943</v>
+        <v>44944</v>
       </c>
       <c r="H53" t="n">
-        <v>1032.7</v>
+        <v>1040.1</v>
       </c>
       <c r="I53" t="n">
         <v>1035.487950102392</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.29</v>
+        <v>-6.05</v>
       </c>
       <c r="L53" t="n">
-        <v>5.98</v>
+        <v>6.19</v>
       </c>
       <c r="M53" t="n">
         <v>1.43</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>5.1</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44971</v>
+        <v>44972</v>
       </c>
       <c r="H54" t="n">
-        <v>1006.75</v>
+        <v>995.4</v>
       </c>
       <c r="I54" t="n">
         <v>998.2717141392855</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.21</v>
+        <v>-4.3</v>
       </c>
       <c r="L54" t="n">
-        <v>4.53</v>
+        <v>4.76</v>
       </c>
       <c r="M54" t="n">
         <v>1</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>6.39</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45021</v>
+        <v>45022</v>
       </c>
       <c r="H55" t="n">
-        <v>997.15</v>
+        <v>1012.1</v>
       </c>
       <c r="I55" t="n">
         <v>999.9336589679807</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.18</v>
+        <v>-1.68</v>
       </c>
       <c r="L55" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="M55" t="n">
         <v>0.73</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.73</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45048</v>
+        <v>45049</v>
       </c>
       <c r="H56" t="n">
-        <v>973.05</v>
+        <v>963.6</v>
       </c>
       <c r="I56" t="n">
         <v>967.5644181647789</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.86</v>
+        <v>-4.79</v>
       </c>
       <c r="L56" t="n">
         <v>5.22</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>5.37</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45076</v>
+        <v>45077</v>
       </c>
       <c r="H57" t="n">
-        <v>959.6</v>
+        <v>975.35</v>
       </c>
       <c r="I57" t="n">
         <v>973.3563394332423</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K57" t="n">
-        <v>0.42</v>
+        <v>-1.22</v>
       </c>
       <c r="L57" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="M57" t="n">
         <v>0.75</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.34</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45229</v>
+        <v>45230</v>
       </c>
       <c r="H58" t="n">
-        <v>1115.2</v>
+        <v>1088.6</v>
       </c>
       <c r="I58" t="n">
         <v>1102.709439947117</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K58" t="n">
-        <v>14.34</v>
+        <v>11.61</v>
       </c>
       <c r="L58" t="n">
         <v>1.5</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>6</v>
+      </c>
+      <c r="U58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>6.5</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45236</v>
+        <v>45237</v>
       </c>
       <c r="H59" t="n">
-        <v>1150</v>
+        <v>1170.95</v>
       </c>
       <c r="I59" t="n">
         <v>1159.372671952344</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.64</v>
+        <v>-7.56</v>
       </c>
       <c r="L59" t="n">
-        <v>5.73</v>
+        <v>7.8</v>
       </c>
       <c r="M59" t="n">
         <v>1.04</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.81</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45398</v>
+        <v>45400</v>
       </c>
       <c r="H60" t="n">
-        <v>1537.55</v>
+        <v>1516.4</v>
       </c>
       <c r="I60" t="n">
         <v>1531.121548808126</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K60" t="n">
-        <v>31.31</v>
+        <v>29.5</v>
       </c>
       <c r="L60" t="n">
         <v>2.08</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>6</v>
+      </c>
+      <c r="U60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>7.18</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45476</v>
+        <v>45477</v>
       </c>
       <c r="H61" t="n">
-        <v>1533.95</v>
+        <v>1557.9</v>
       </c>
       <c r="I61" t="n">
         <v>1553.008449001088</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.16</v>
+        <v>-2.74</v>
       </c>
       <c r="L61" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="M61" t="n">
         <v>2.51</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.55</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45587</v>
+        <v>45588</v>
       </c>
       <c r="H62" t="n">
-        <v>1887.55</v>
+        <v>1839.35</v>
       </c>
       <c r="I62" t="n">
         <v>1849.338783346731</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K62" t="n">
-        <v>21.16</v>
+        <v>18.07</v>
       </c>
       <c r="L62" t="n">
         <v>2.05</v>
@@ -3975,7 +4718,7 @@
         <v>1.18</v>
       </c>
       <c r="N62" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="O62" t="n">
         <v>1.56</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.94</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="H63" t="n">
-        <v>1861.25</v>
+        <v>1883.9</v>
       </c>
       <c r="I63" t="n">
         <v>1873.062503326965</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.19</v>
+        <v>-2.42</v>
       </c>
       <c r="L63" t="n">
         <v>4.53</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>5.86</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H64" t="n">
-        <v>1826.35</v>
+        <v>1784.8</v>
       </c>
       <c r="I64" t="n">
         <v>1789.838101577445</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.05</v>
+        <v>-5.26</v>
       </c>
       <c r="L64" t="n">
-        <v>3.71</v>
+        <v>5.9</v>
       </c>
       <c r="M64" t="n">
         <v>0.38</v>
       </c>
       <c r="N64" t="n">
-        <v>1.51</v>
+        <v>2.28</v>
       </c>
       <c r="O64" t="n">
         <v>1.22</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.92</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45729</v>
+        <v>45733</v>
       </c>
       <c r="H65" t="n">
-        <v>1683.45</v>
+        <v>1704.3</v>
       </c>
       <c r="I65" t="n">
         <v>1697.376052030355</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K65" t="n">
-        <v>5.68</v>
+        <v>4.51</v>
       </c>
       <c r="L65" t="n">
         <v>3.27</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>6.82</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H66" t="n">
-        <v>1709.35</v>
+        <v>1666.35</v>
       </c>
       <c r="I66" t="n">
         <v>1682.655257238693</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3</v>
+        <v>-2.23</v>
       </c>
       <c r="L66" t="n">
-        <v>2.71</v>
+        <v>4.94</v>
       </c>
       <c r="M66" t="n">
-        <v>0.45</v>
+        <v>5.22</v>
       </c>
       <c r="N66" t="n">
         <v>3.43</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>9.41</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45772</v>
+        <v>45775</v>
       </c>
       <c r="H67" t="n">
-        <v>1787.4</v>
+        <v>1841.6</v>
       </c>
       <c r="I67" t="n">
         <v>1823.071592303715</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K67" t="n">
-        <v>-7.26</v>
+        <v>-10.52</v>
       </c>
       <c r="L67" t="n">
-        <v>8.949999999999999</v>
+        <v>10.78</v>
       </c>
       <c r="M67" t="n">
         <v>3.5</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45786</v>
+        <v>45789</v>
       </c>
       <c r="H68" t="n">
-        <v>1744.8</v>
+        <v>1686.2</v>
       </c>
       <c r="I68" t="n">
         <v>1698.481569350103</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K68" t="n">
-        <v>-5.26</v>
+        <v>-8.44</v>
       </c>
       <c r="L68" t="n">
-        <v>5.97</v>
+        <v>11.84</v>
       </c>
       <c r="M68" t="n">
-        <v>0.9</v>
+        <v>2.81</v>
       </c>
       <c r="N68" t="n">
-        <v>2.08</v>
+        <v>3.36</v>
       </c>
       <c r="O68" t="n">
         <v>3.03</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>7.88</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="H69" t="n">
-        <v>1648.6</v>
+        <v>1656</v>
       </c>
       <c r="I69" t="n">
         <v>1655.338799216679</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K69" t="n">
-        <v>2.23</v>
+        <v>1.79</v>
       </c>
       <c r="L69" t="n">
         <v>4.67</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>4.49</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="H70" t="n">
-        <v>1792.9</v>
+        <v>1745.9</v>
       </c>
       <c r="I70" t="n">
         <v>1748.589936606221</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K70" t="n">
-        <v>8.27</v>
+        <v>5.43</v>
       </c>
       <c r="L70" t="n">
         <v>6.52</v>
@@ -4431,7 +5270,7 @@
         <v>2.61</v>
       </c>
       <c r="N70" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O70" t="n">
         <v>0.45</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>5.76</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H71" t="n">
-        <v>1707.8</v>
+        <v>1711.1</v>
       </c>
       <c r="I71" t="n">
         <v>1709.319542739657</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K71" t="n">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="L71" t="n">
         <v>3.48</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>6.04</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="H72" t="n">
-        <v>1757.2</v>
+        <v>1728.5</v>
       </c>
       <c r="I72" t="n">
         <v>1731.037187863808</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K72" t="n">
-        <v>2.69</v>
+        <v>1.02</v>
       </c>
       <c r="L72" t="n">
         <v>1.03</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>8.42</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="H73" t="n">
-        <v>1747.3</v>
+        <v>1778.7</v>
       </c>
       <c r="I73" t="n">
         <v>1772.111727679517</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.09</v>
+        <v>-2.9</v>
       </c>
       <c r="L73" t="n">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="M73" t="n">
         <v>1.38</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>9.24</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="H74" t="n">
-        <v>1930</v>
+        <v>1882</v>
       </c>
       <c r="I74" t="n">
         <v>1910.597447767283</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K74" t="n">
-        <v>8.51</v>
+        <v>5.81</v>
       </c>
       <c r="L74" t="n">
         <v>1.61</v>
@@ -4659,7 +5546,7 @@
         <v>1.22</v>
       </c>
       <c r="N74" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="O74" t="n">
         <v>1.8</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>7.06</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="H75" t="n">
-        <v>1920</v>
+        <v>1984.8</v>
       </c>
       <c r="I75" t="n">
         <v>1982.65447597365</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K75" t="n">
-        <v>-2.02</v>
+        <v>-5.46</v>
       </c>
       <c r="L75" t="n">
-        <v>3.6</v>
+        <v>5.46</v>
       </c>
       <c r="M75" t="n">
         <v>0.78</v>
       </c>
       <c r="N75" t="n">
-        <v>1.33</v>
+        <v>3.37</v>
       </c>
       <c r="O75" t="n">
         <v>-2.49</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>7.3</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H76" t="n">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="I76" t="n">
         <v>1839.9250352071</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K76" t="n">
-        <v>-7.3</v>
+        <v>-7.55</v>
       </c>
       <c r="L76" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="M76" t="n">
         <v>1.09</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,14 @@
       <c r="Q77" t="n">
         <v>30</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9791,7 +10722,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.2</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="6">
@@ -9801,7 +10732,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -9811,7 +10742,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8">
@@ -9821,7 +10752,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9831,7 +10762,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="10">
@@ -9841,7 +10772,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>121.6</v>
+        <v>122.6</v>
       </c>
     </row>
     <row r="11">
@@ -9851,7 +10782,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -9861,7 +10792,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -9871,7 +10802,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="14">
@@ -9881,7 +10812,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.18</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="15">
@@ -9891,7 +10822,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.75</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="16">
@@ -9901,7 +10832,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.58</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="17">
@@ -9911,7 +10842,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.31</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="18">
@@ -9921,7 +10852,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="19">
@@ -9931,7 +10862,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.1</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="20">
@@ -9941,7 +10872,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.75</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="21">
@@ -9951,7 +10882,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.66</v>
+        <v>19.67</v>
       </c>
     </row>
     <row r="22">
@@ -9961,7 +10892,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
@@ -9971,7 +10902,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -9981,7 +10912,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="25">
@@ -9991,7 +10922,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -10001,7 +10932,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.36</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="27">
@@ -10011,7 +10942,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.43</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="28">
@@ -10021,7 +10952,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
